--- a/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
+++ b/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
@@ -1594,14 +1594,14 @@
       </c>
       <c r="FP3" t="inlineStr">
         <is>
-          <t>Notarztstandort Saarbrücken Rastpfuhl 1/9, 2, Rheinstraße, Rastpfuhl, Malstatt, West, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66113, Deutschland</t>
+          <t>Rheinstr. 6, 66115 Saarbrücken, 2, Rheinstraße, Rastpfuhl, Malstatt, West, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66113, Deutschland</t>
         </is>
       </c>
       <c r="FQ3" t="n">
-        <v>49.2486598</v>
+        <v>49.2475551</v>
       </c>
       <c r="FR3" t="n">
-        <v>6.9597177</v>
+        <v>6.9599699</v>
       </c>
     </row>
     <row r="4">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="FP4" t="inlineStr">
         <is>
-          <t>Dr. med. Anne Benn Lembert, 76-78, Bahnhofstraße, Hauptbahnhof, St. Johann, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66111, Deutschland</t>
+          <t>Aktiv-Ortho, 76-78, Bahnhofstraße, Hauptbahnhof, St. Johann, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66111, Deutschland</t>
         </is>
       </c>
       <c r="FQ4" t="n">
-        <v>49.2370854</v>
+        <v>49.2371047</v>
       </c>
       <c r="FR4" t="n">
-        <v>6.9925905</v>
+        <v>6.9925617</v>
       </c>
     </row>
     <row r="5">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="FQ5" t="n">
-        <v>49.2212209</v>
+        <v>49.2209533</v>
       </c>
       <c r="FR5" t="n">
-        <v>6.994143</v>
+        <v>6.9965189</v>
       </c>
     </row>
     <row r="6">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="FQ7" t="n">
-        <v>49.2003929</v>
+        <v>49.2003263</v>
       </c>
       <c r="FR7" t="n">
-        <v>7.0114755</v>
+        <v>7.0111408</v>
       </c>
     </row>
     <row r="8">

--- a/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
+++ b/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
@@ -1594,14 +1594,14 @@
       </c>
       <c r="FP3" t="inlineStr">
         <is>
-          <t>Notarztstandort Saarbrücken Rastpfuhl 1/9, 2, Rheinstraße, Rastpfuhl, Malstatt, West, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66113, Deutschland</t>
+          <t>Rheinstr. 6, 66115 Saarbrücken, 2, Rheinstraße, Rastpfuhl, Malstatt, West, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66113, Deutschland</t>
         </is>
       </c>
       <c r="FQ3" t="n">
-        <v>49.2486598</v>
+        <v>49.2475551</v>
       </c>
       <c r="FR3" t="n">
-        <v>6.9597177</v>
+        <v>6.9599699</v>
       </c>
     </row>
     <row r="4">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="FP4" t="inlineStr">
         <is>
-          <t>Dr. med. Anne Benn Lembert, 76-78, Bahnhofstraße, Hauptbahnhof, St. Johann, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66111, Deutschland</t>
+          <t>Aktiv-Ortho, 76-78, Bahnhofstraße, Hauptbahnhof, St. Johann, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66111, Deutschland</t>
         </is>
       </c>
       <c r="FQ4" t="n">
-        <v>49.2370854</v>
+        <v>49.2371047</v>
       </c>
       <c r="FR4" t="n">
-        <v>6.9925905</v>
+        <v>6.9925617</v>
       </c>
     </row>
     <row r="5">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="FQ5" t="n">
-        <v>49.2212209</v>
+        <v>49.2209533</v>
       </c>
       <c r="FR5" t="n">
-        <v>6.994143</v>
+        <v>6.9965189</v>
       </c>
     </row>
     <row r="6">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="FQ7" t="n">
-        <v>49.2003929</v>
+        <v>49.2003263</v>
       </c>
       <c r="FR7" t="n">
-        <v>7.0114755</v>
+        <v>7.0111408</v>
       </c>
     </row>
     <row r="8">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="FP24" t="inlineStr">
         <is>
-          <t>Psychosomatische Klinik Berus, 55, Orannastraße, Berus, Überherrn, Landkreis Saarlouis, Saarland, 66802, Deutschland</t>
+          <t>55, Orannastraße, Berus, Überherrn, Landkreis Saarlouis, Saarland, 66802, Deutschland</t>
         </is>
       </c>
       <c r="FQ24" t="n">

--- a/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
+++ b/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
@@ -1594,14 +1594,14 @@
       </c>
       <c r="FP3" t="inlineStr">
         <is>
-          <t>Rheinstr. 6, 66115 Saarbrücken, 2, Rheinstraße, Rastpfuhl, Malstatt, West, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66113, Deutschland</t>
+          <t>2, Rheinstraße, Rastpfuhl, Malstatt, West, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66113, Deutschland</t>
         </is>
       </c>
       <c r="FQ3" t="n">
-        <v>49.2475551</v>
+        <v>49.2476879</v>
       </c>
       <c r="FR3" t="n">
-        <v>6.9599699</v>
+        <v>6.9595153</v>
       </c>
     </row>
     <row r="4">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="FP4" t="inlineStr">
         <is>
-          <t>Aktiv-Ortho, 76-78, Bahnhofstraße, Hauptbahnhof, St. Johann, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66111, Deutschland</t>
+          <t>Dr. med. Anne Benn Lembert, 76-78, Bahnhofstraße, Hauptbahnhof, St. Johann, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66111, Deutschland</t>
         </is>
       </c>
       <c r="FQ4" t="n">
-        <v>49.2371047</v>
+        <v>49.2370854</v>
       </c>
       <c r="FR4" t="n">
-        <v>6.9925617</v>
+        <v>6.9925905</v>
       </c>
     </row>
     <row r="5">
@@ -2116,14 +2116,14 @@
       </c>
       <c r="FP5" t="inlineStr">
         <is>
-          <t>1, Winterberg, St. Arnual, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66119, Deutschland</t>
+          <t>Behandlungsbau, 1, Winterberg, St. Arnual, Bezirk Mitte, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66119, Deutschland</t>
         </is>
       </c>
       <c r="FQ5" t="n">
-        <v>49.2209533</v>
+        <v>49.2211468</v>
       </c>
       <c r="FR5" t="n">
-        <v>6.9965189</v>
+        <v>6.9972072</v>
       </c>
     </row>
     <row r="6">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="FP7" t="inlineStr">
         <is>
-          <t>Haus 1, 10, Sonnenbergstraße, Irgenhöhe, Schönbach, Güdingen, Bezirk Halberg, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66119, Deutschland</t>
+          <t>10, Sonnenbergstraße, Irgenhöhe, Schönbach, Güdingen, Bezirk Halberg, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66119, Deutschland</t>
         </is>
       </c>
       <c r="FQ7" t="n">
-        <v>49.2003263</v>
+        <v>49.2005146</v>
       </c>
       <c r="FR7" t="n">
-        <v>7.0111408</v>
+        <v>7.0133027</v>
       </c>
     </row>
     <row r="8">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="FP14" t="inlineStr">
         <is>
-          <t>148, Trierer Straße, Merzig, Landkreis Merzig-Wadern, Saarland, 66663, Deutschland</t>
+          <t>148i, Trierer Straße, Merzig, Landkreis Merzig-Wadern, Saarland, 66663, Deutschland</t>
         </is>
       </c>
       <c r="FQ14" t="n">
-        <v>49.4571859</v>
+        <v>49.4590255</v>
       </c>
       <c r="FR14" t="n">
-        <v>6.6315777</v>
+        <v>6.6299114</v>
       </c>
     </row>
     <row r="15">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="FP24" t="inlineStr">
         <is>
-          <t>55, Orannastraße, Berus, Überherrn, Landkreis Saarlouis, Saarland, 66802, Deutschland</t>
+          <t>Median Klinik Berus, 55, Orannastraße, Berus, Überherrn, Landkreis Saarlouis, Saarland, 66802, Deutschland</t>
         </is>
       </c>
       <c r="FQ24" t="n">

--- a/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
+++ b/src/index_travel_accessibility/data/processed/saarland_hospitals_with_coords.xlsx
@@ -2620,14 +2620,14 @@
       </c>
       <c r="FP7" t="inlineStr">
         <is>
-          <t>Haus 1, 10, Sonnenbergstraße, Irgenhöhe, Schönbach, Güdingen, Bezirk Halberg, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66119, Deutschland</t>
+          <t>SHG Kliniken Sonnenberg, 10, Sonnenbergstraße, Irgenhöhe, Schönbach, Güdingen, Bezirk Halberg, Saarbrücken, Regionalverband Saarbrücken, Saarland, 66119, Deutschland</t>
         </is>
       </c>
       <c r="FQ7" t="n">
-        <v>49.2003929</v>
+        <v>49.20101</v>
       </c>
       <c r="FR7" t="n">
-        <v>7.0114755</v>
+        <v>7.0111263</v>
       </c>
     </row>
     <row r="8">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="FP24" t="inlineStr">
         <is>
-          <t>Psychosomatische Klinik Berus, 55, Orannastraße, Berus, Überherrn, Landkreis Saarlouis, Saarland, 66802, Deutschland</t>
+          <t>Median Klinik Berus, 55, Orannastraße, Berus, Überherrn, Landkreis Saarlouis, Saarland, 66802, Deutschland</t>
         </is>
       </c>
       <c r="FQ24" t="n">
